--- a/reports/Debug-purgatory-20260105/Month to Date (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260105/Month to Date (Actual)_Visits.xlsx
@@ -34,13 +34,13 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
+    <t>Purgatory Uplift Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
     <t>Purgatory Coaster</t>
@@ -507,7 +507,7 @@
         <v>46023</v>
       </c>
       <c r="C7" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -521,7 +521,7 @@
         <v>46023</v>
       </c>
       <c r="C8" s="2">
-        <v>1552</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -535,7 +535,7 @@
         <v>46023</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -546,10 +546,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C10" s="2">
-        <v>9</v>
+        <v>1445</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -560,10 +560,10 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C11" s="2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -577,7 +577,7 @@
         <v>46026</v>
       </c>
       <c r="C12" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -591,7 +591,7 @@
         <v>46027</v>
       </c>
       <c r="C13" s="2">
-        <v>13</v>
+        <v>564</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,13 +602,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C14" s="2">
-        <v>322</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -619,10 +619,10 @@
         <v>46023</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>1552</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -633,10 +633,10 @@
         <v>46023</v>
       </c>
       <c r="C16" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,7 +647,7 @@
         <v>46023</v>
       </c>
       <c r="C17" s="2">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -658,10 +658,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C18" s="2">
-        <v>1445</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C20" s="2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -703,10 +703,10 @@
         <v>46027</v>
       </c>
       <c r="C21" s="2">
-        <v>564</v>
+        <v>322</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -717,10 +717,10 @@
         <v>46023</v>
       </c>
       <c r="C22" s="2">
-        <v>56</v>
+        <v>528</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>936</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>5</v>
@@ -745,7 +745,7 @@
         <v>46024</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -759,7 +759,7 @@
         <v>46024</v>
       </c>
       <c r="C25" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -770,10 +770,10 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C26" s="2">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,13 +784,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C27" s="2">
-        <v>406</v>
+        <v>311</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C28" s="2">
-        <v>2</v>
+        <v>969</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C29" s="2">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C30" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -857,10 +857,10 @@
         <v>46024</v>
       </c>
       <c r="C32" s="2">
-        <v>608</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C33" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -885,10 +885,10 @@
         <v>46025</v>
       </c>
       <c r="C34" s="2">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -899,10 +899,10 @@
         <v>46025</v>
       </c>
       <c r="C35" s="2">
-        <v>1469</v>
+        <v>1099</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C36" s="2">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C37" s="2">
-        <v>906</v>
+        <v>3</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -952,13 +952,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C40" s="2">
-        <v>17</v>
+        <v>1455</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -994,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C42" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1008,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C43" s="2">
-        <v>1456</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1022,10 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C44" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C45" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,7 +1050,7 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -1064,13 +1064,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>1407</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C48" s="2">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -1106,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C50" s="2">
-        <v>1408</v>
+        <v>608</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46027</v>
+        <v>46024</v>
       </c>
       <c r="C51" s="2">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C53" s="2">
-        <v>14</v>
+        <v>1469</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C54" s="2">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1176,13 +1176,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>906</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C56" s="2">
-        <v>310</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C57" s="2">
-        <v>1100</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1221,10 +1221,10 @@
         <v>46027</v>
       </c>
       <c r="C58" s="2">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C59" s="2">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,13 +1246,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C60" s="2">
-        <v>528</v>
+        <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C61" s="2">
-        <v>936</v>
+        <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1277,7 +1277,7 @@
         <v>46024</v>
       </c>
       <c r="C62" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1291,7 +1291,7 @@
         <v>46024</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>5</v>
@@ -1305,10 +1305,10 @@
         <v>46025</v>
       </c>
       <c r="C64" s="2">
-        <v>34</v>
+        <v>406</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1316,13 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C65" s="2">
-        <v>311</v>
+        <v>2</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C66" s="2">
-        <v>969</v>
+        <v>2</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>5</v>
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C67" s="2">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
